--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
+          <t>Software Engineer AIML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, XGBoost, BigQuery, CI/CD, Jenkins, Terraform, Git, BigQuery</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, Kubernetes, AKS, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
+          <t>https://www.indeed.com/viewjob?jk=716a90ad671df648</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Completions &amp; Well Management Research Engineer - Advanced</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, Git, Databricks, Power BI, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,287 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=67a37e0d3a0ff599</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, AWS SageMaker, GCP Vertex AI, Azure ML, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Principle Data Scientist</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Coca-Cola Company</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Azure ML, Synapse, Git, Databricks, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cccbea100f2ca16</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>propio</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e27050387795d89a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI Integration &amp; Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Inver Grove Heights, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LangChain, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a23d524d615e8124</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Propio LS LLC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a113c3248d344aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ellipsis Health</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Movi Healthcare</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Charleston, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS SageMaker, Data Lake, Docker, CI/CD, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3420442aed030eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The Coca-Cola Company</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81b499173e817d46</t>
+          <t>https://www.indeed.com/viewjob?jk=0af16c460096d8c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer AIML</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, Kubernetes, AKS, CI/CD, Python, SQL</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716a90ad671df648</t>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Completions &amp; Well Management Research Engineer - Advanced</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,52 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Power BI, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a37e0d3a0ff599</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0af16c460096d8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f210119310b3daee</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,287 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AI-Native Builder- EST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Care Innovation - Senior Solution Engineer 135-2034</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CommunityCare</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=925044a0aee662dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Care Innovation - Senior Solution Architect 136-2001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CommunityCare</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66441702cc6d80c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HealthDrive</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Synapse, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d5ac24333bc87ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Care Innovation - Automation Engineer 136-2000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CommunityCare</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f210119310b3daee</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aba40345cbde0f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4207b8497b2b9a18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f2eab6b68c3c90</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, Data Lake, Kubernetes, Apache Airflow, CI/CD, Git, PySpark, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Danbury, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Docker, Tableau, Matplotlib, Seaborn, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a855ea42b12c1b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Care Innovation - Senior Solution Engineer 135-2034</t>
+          <t>Data scientist III View Jobs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CommunityCare</t>
+          <t>Swiggy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Capitol, MT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, PySpark, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925044a0aee662dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7841efff777aa9f9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Care Innovation - Senior Solution Architect 136-2001</t>
+          <t>Data Scientist 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CommunityCare</t>
+          <t>DAIKIN COMFORT TECHNOLOGIES MFG INC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Waller, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66441702cc6d80c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8c5ddf28842b6a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HealthDrive</t>
+          <t>Online Taxes, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Synapse, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5ac24333bc87ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fe389bf2e2ebdf52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Care Innovation - Automation Engineer 136-2000</t>
+          <t>Cloud DevOps and AI Security Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CommunityCare</t>
+          <t>Renesas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba40345cbde0f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Smart Apply Test Company</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b8497b2b9a18</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Smart Apply Test Company</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f2eab6b68c3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=6db3db9a5aed6022</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>AI/ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kubernetes, Apache Airflow, CI/CD, Git, PySpark, Kafka, Hadoop</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer II - AI Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Danbury, CT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Tableau, Matplotlib, Seaborn, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a855ea42b12c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a006132fbd4571bf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data scientist III View Jobs</t>
+          <t>Solutions Integration Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiggy</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Capitol, MT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, PySpark, Python, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,112 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7841efff777aa9f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Data Scientist 3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DAIKIN COMFORT TECHNOLOGIES MFG INC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Waller, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8c5ddf28842b6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Online Taxes, Inc.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe389bf2e2ebdf52</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cloud DevOps and AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Renesas</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6db3db9a5aed6022</t>
+          <t>https://www.indeed.com/viewjob?jk=739f0eb98945e450</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Engineer</t>
+          <t>Sr. AI Engineer - Remote or Hybrid in Eden Prairie, MN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=77e3a68595d984e4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Sr AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=57afb297c8c065a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer II - AI Platform</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a006132fbd4571bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Redshift, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,602 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=739f0eb98945e450</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TSOLife</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Security Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fidelity National Financial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423c7cd2db319b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer - AI Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Consumer Reports</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc1fa58aa08fc10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Exadel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Exadel</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Burr Ridge, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6899faaac3d2746e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d3ca6a9cc6731bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d84e44e1235a07b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; IT Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cellular Intelligence</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f22cb91afe4dd45</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Research</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hippocratic AI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Terraform, Hadoop, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=331b3266d01e6668</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97ccf29c400390fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=571de53a544ec96c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ce77bbd687e3679</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f9a55acfa11c5f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab5722f9be9558d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Developer, AI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ACCO Engineered Systems</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d95641a713780602</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist 1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DAIKIN COMFORT TECHNOLOGIES MFG INC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Waller, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da835f35750d69cf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer - Remote or Hybrid in Eden Prairie, MN</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>Data Scientist, RAG, S3, Redshift, BigQuery, Data Lake, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e3a68595d984e4</t>
+          <t>https://www.indeed.com/viewjob?jk=335286c429f8d5b7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote</t>
+          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker</t>
+          <t>RAG, Azure ML, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57afb297c8c065a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, PostgreSQL, MySQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Redshift</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, PostgreSQL, MySQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
+          <t>Senior Security Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TSOLife</t>
+          <t>Fidelity National Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL</t>
+          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
+          <t>https://www.indeed.com/viewjob?jk=441225f3af65f344</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Security Automation Engineer</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fidelity National Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423c7cd2db319b06</t>
+          <t>https://www.indeed.com/viewjob?jk=96c4f941b3b74b9a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - AI Applications</t>
+          <t>IIB and MQ Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumer Reports</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, FastAPI, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc1fa58aa08fc10</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Quantum Integrations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Infleqtion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MySQL, Python</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=583a9dc43d30a84f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Quantum Integrations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Infleqtion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, PostgreSQL, MySQL, Python</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=81a03862cda1e6e6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Software Engineer, Transformation Acceleration Group</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burr Ridge, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6899faaac3d2746e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e84ba557b474467</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Data Scientist, OT Security</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3ca6a9cc6731bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff4d963f0dcfc90</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>CANDID</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, S3, MLflow, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84e44e1235a07b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3276b801b81e99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; IT Systems Engineer</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cellular Intelligence</t>
+          <t>Minted</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Julia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f22cb91afe4dd45</t>
+          <t>https://www.indeed.com/viewjob?jk=a49df65a4fa8bf16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Research</t>
+          <t>Senior Software Engineer - GraphAware Hume</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hippocratic AI</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Terraform, Hadoop, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331b3266d01e6668</t>
+          <t>https://www.indeed.com/viewjob?jk=cd5f675d3a94e967</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Victra-Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ccf29c400390fa</t>
+          <t>https://www.indeed.com/viewjob?jk=64b0a1adf5c0f698</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, MLflow, Docker, CI/CD, Jenkins, Git, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571de53a544ec96c</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Engineer, AI Application Development</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Weil, Gotshal &amp; Manges LLP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, FastAPI, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce77bbd687e3679</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbfd3f7a6a4b60f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh-Durham, NC, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9a55acfa11c5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4ff40d96620c2d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5722f9be9558d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0dd2cede54aeb05c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Developer, AI</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ACCO Engineered Systems</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95641a713780602</t>
+          <t>https://www.indeed.com/viewjob?jk=d8eb3ab641e50773</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist 1</t>
+          <t>Sr. Engineer - Software Development Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DAIKIN COMFORT TECHNOLOGIES MFG INC</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Waller, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,112 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da835f35750d69cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CounterFind</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Copilot, FastAPI, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bb003d1b65f3ab5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr Decision Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fractal Analytics</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92df10f79cc784e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SharkNinja</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Needham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f07af7ebf3d36e24</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-24.xlsx
+++ b/daily_matches/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, BigQuery, Data Lake, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=335286c429f8d5b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7577dbded714e8d0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
+          <t>Senior IT Data Engineer (R0465160 Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
+          <t>RAG, BigQuery, Docker, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a34cdd4d3ae0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, PostgreSQL, MySQL, Power BI, Python</t>
+          <t>RAG, Copilot, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, PostgreSQL, MySQL, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=333082b4818fe4f3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Security Automation Engineer</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fidelity National Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441225f3af65f344</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Quincy Credit Union</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>Cortex, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c4f941b3b74b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=50d00d448b08684f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IIB and MQ Platform Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, MySQL, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
+          <t>https://www.indeed.com/viewjob?jk=3f909203341f23bc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quantum Integrations Engineer</t>
+          <t>Software Engineer – Independent Contractor / Project-Based (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Infleqtion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, PostgreSQL, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583a9dc43d30a84f</t>
+          <t>https://www.indeed.com/viewjob?jk=671885b17b760d63</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Quantum Integrations Engineer</t>
+          <t>Senior Associate Solutions Designer, AI Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Infleqtion</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a03862cda1e6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e2039faf7b2ee1d3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Transformation Acceleration Group</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Data Lake, Docker, Kubernetes, AKS, CI/CD, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e84ba557b474467</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fbfce630a64832</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist, OT Security</t>
+          <t>Software Engineer - AI Platform, Business Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff4d963f0dcfc90</t>
+          <t>https://www.indeed.com/viewjob?jk=f0787747f03e42de</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer- Devices Cloud Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CANDID</t>
+          <t>Brivo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, S3, MLflow, CI/CD, Terraform, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3276b801b81e99</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbd8f33418b427</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minted</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Julia</t>
+          <t>RAG, S3, FastAPI, Kafka, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49df65a4fa8bf16</t>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GraphAware Hume</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Trust &amp; Will</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, AKS, Git, Snowflake, Polars, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5f675d3a94e967</t>
+          <t>https://www.indeed.com/viewjob?jk=fa02c09dcca38f84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Engineering Manger - Dev Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Victra-Verizon Authorized Retailer</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, Git, Python, R, Java</t>
+          <t>Generative AI, FastAPI, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b0a1adf5c0f698</t>
+          <t>https://www.indeed.com/viewjob?jk=32c8818a75bea6ca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Senior Data Engineer- People Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, MLflow, Docker, CI/CD, Jenkins, Git, MongoDB, Python, R</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, Git, Snowflake, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c08d6c8adde9080</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI Application Development</t>
+          <t>AI Engineer - AIT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Weil, Gotshal &amp; Manges LLP</t>
+          <t>Boston Children's Hospital</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbfd3f7a6a4b60f</t>
+          <t>https://www.indeed.com/viewjob?jk=aea27098d7bb9a3f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer Technician - R&amp;D and Automation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
+          <t>RAG, OpenCV, S3, EC2, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4ff40d96620c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=444a63e7dab6104e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dd2cede54aeb05c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cc8c8f890e031a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>The Mosaic Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
+          <t>Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8eb3ab641e50773</t>
+          <t>https://www.indeed.com/viewjob?jk=da4303c89e8fda6a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Software Development Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>AG Mednet Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, S3, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=257cd4a70ce7d655</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-Stack Engineering Intern</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CounterFind</t>
+          <t>Reach Media LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Copilot, FastAPI, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb003d1b65f3ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac6c052c0b85c2b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Decision Scientist</t>
+          <t>IPM Technology Architect - Generative AI &amp; Insurance Solutions - 00070258051</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92df10f79cc784e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SharkNinja</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Needham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f07af7ebf3d36e24</t>
+          <t>https://www.indeed.com/viewjob?jk=b562f57314fbd29d</t>
         </is>
       </c>
     </row>
